--- a/docs/exports/SQ1_Yesly_Backend_Clarifications_Questionaire.xlsx
+++ b/docs/exports/SQ1_Yesly_Backend_Clarifications_Questionaire.xlsx
@@ -57,7 +57,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="27" max="27" width="44" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -71,19 +71,19 @@
           <t xml:space="preserve">Comments</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr" s="1">
+      <c r="C1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -98,12 +98,12 @@
           <t xml:space="preserve">One active session per user. A new OTP login on a second device revokes the first device's refresh token; the first device shows "you signed in on another device" and returns to A02. No two concurrent sessions.</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">A02, FE-07</t>
         </is>
@@ -120,12 +120,12 @@
           <t xml:space="preserve">Deletion is S25 from H09: confirm, a cooling period during which the request can be withdrawn (config; 7 days as the placeholder), then personal data is erased. Regulated records are retained under restricted access for the period Compliance names: the KYC record, the signed agreement, consent records, plan snapshots (plan_input_version, the advice record), invoices and payment references, call records. The DPDP notice on H09 says so. to be decided: the retention period and the exact retained-record list (W05, owner Compliance).</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr" s="2">
+      <c r="C3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">H09, S25, W05</t>
         </is>
@@ -142,12 +142,12 @@
           <t xml:space="preserve">Already decided on the board. The consent asks fetch-now plus quarterly for the review (A05, A06: 12 months, read-only). A refresh shows the diff first and asks "we updated N numbers, good to go?" (A08, Q01). A manual override locks the field, so a refresh never overwrites it unless the person unlocks it (A08). Every value carries its source (AA-fed, CAS-verified, manual) and its as-of date. Sell and switch advice only on AA-fed or CAS-verified holdings; manual entries get buy advice only (A05). Q05 lets the person update any number at any time; Q06 reopens only the screens a life event touches.</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">A05, A06, A08, Q01, Q05, Q06</t>
         </is>
@@ -164,14 +164,19 @@
           <t xml:space="preserve">Data in: the Account Aggregator (Finvu, I01) and the CAS upload (A10b) only; the app never connects to a broker or a platform directly. Execution out: BSE StAR MF for mutual funds (I02) and smallcase Gateway for stocks, ETFs and REITs through the person's own broker (I03; the supported broker list is Gateway's: to be verified from its documentation). Per connection the app shows: institution, masked account, as-of date, consent valid till, status (connected, failed, stale, expired), include or exclude (A08 fields; consent_status, consent_valid_till, fetch_frequency and last_fetch_at per FIP).</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">open - to be decided</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">I01, I02, I03, A08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
@@ -186,12 +191,12 @@
           <t xml:space="preserve">HoA's eight-question RPQ (D08a to D08h), tap only; the band comes from the score (D09); the annual re-confirmation is Q04. The scoring map is a table HoA owes (gap G06, W30, owner Investment advisory); it is config, not code.</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">D08a, D09, Q04, W30</t>
         </is>
@@ -208,12 +213,12 @@
           <t xml:space="preserve">Harish, through the logic panel: L04 holds the instrument universe (ISINs), L03 the buckets and cohorts, L09 the constraints, L05 the staging area with impact preview, L06 publish. Nothing reaches a person unpublished; a publish triggers plan updates (S11, H05). There is no per-user approval and no human review gate on plan generation: advisers change inputs and the engine re-runs. (L00 to L09 are open on the board only for their table shapes, W04.)</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr" s="2">
+      <c r="C7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">L03, L04, L05, L06, L09, S11, H05</t>
         </is>
@@ -230,12 +235,12 @@
           <t xml:space="preserve">No in-app audio or video is built. K02 carries a join link from the CRM's meeting tool, or a phone number when there is no link. The meeting tool (I24, W32, owner Admin) and the recording consent and retention rule (W33, owner Compliance) are open; K02 and K06 stay open until then.</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr" s="2">
+      <c r="C8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">K02, K06, I24, W32, W33</t>
         </is>
@@ -252,12 +257,12 @@
           <t xml:space="preserve">Not in scope. A credit is a whole call: calls_included_per_period against calls_used (K01). Call length is config (to be verified: the recipe, W31). No metering by minutes, no automatic ending, no top-up during a call.</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr" s="2">
+      <c r="C9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">K01, W31</t>
         </is>
@@ -274,12 +279,12 @@
           <t xml:space="preserve">Prepaid, always. Included calls come with the subscription; an a la carte call is a single charge through P04 before the slot picker opens (K04, then K05). There is nothing to collect after a call; deleting the app changes nothing.</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr" s="2">
+      <c r="C10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">K04, K05, P04</t>
         </is>
@@ -296,12 +301,12 @@
           <t xml:space="preserve">HoA's own call centre; no external adviser network. The capacity number and the slot design are HoA's (gap G04, W31).</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr" s="2">
+      <c r="C11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">K05, W31</t>
         </is>
@@ -318,12 +323,12 @@
           <t xml:space="preserve">No list and no name. Any available adviser from the call centre takes any call (K05). The adviser-continuity flag is config, off by default; when on, a chip asks for the same adviser as last time.</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr" s="2">
+      <c r="C12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">K05</t>
         </is>
@@ -340,12 +345,12 @@
           <t xml:space="preserve">Slots come from Zoho Bookings (I14): one adviser, one call at a time. No slot within 7 days shows a waitlist and creates a call-centre task (K05). A no-show follows S20: rebook, nudges at 1 hour and 24 hours, a task after the second no-show. The number of advisers and their hours is W31.</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr" s="2">
+      <c r="C13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">K05, S20, I14, W31</t>
         </is>
@@ -362,12 +367,12 @@
           <t xml:space="preserve">Yes. The booking creates the event in Zoho Bookings and the adviser's calendar and returns the join link; the app shows the slot and the link on K02; the confirmation goes by push, WhatsApp and email per the ladder; the call centre sees the plan (G03) and the inputs (D10) before the call (M01).</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr" s="2">
+      <c r="C14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">K02, I14, M01</t>
         </is>
@@ -384,12 +389,12 @@
           <t xml:space="preserve">to be decided: the cancellation and refund rule (brief H5), owner Compliance with Harish (W05). What the board already fixes: cancel is always allowed from Q03a with no reason required; the plan stays readable and refresh stops; pause is offered; a refund request creates a CRM task with the payment reference and lands in S24; the rule itself is a parameter. Note for Compliance: SEBI's investment-adviser fee rules already shape the answer (a refund of the unexpired period on termination, a capped breakage amount); the exact wording is theirs.</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr" s="2">
+      <c r="C15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">open - to be decided: the cancellation and refund rule (brief H5), owner Compliance with Harish (W05)</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">Q03a, S24, W05</t>
         </is>
@@ -406,12 +411,12 @@
           <t xml:space="preserve">The adviser writes the summary in the CRM as structured notes: the inputs that change (which re-run the plan) and a short note. The app shows them on K03, and H05 shows the plan diff. No automated transcription or AI summary in V1; that waits for the recording rule (W33).</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr" s="2">
+      <c r="C16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">K03, H05, W33</t>
         </is>

--- a/docs/exports/SQ1_Yesly_Backend_Clarifications_Questionaire.xlsx
+++ b/docs/exports/SQ1_Yesly_Backend_Clarifications_Questionaire.xlsx
@@ -161,7 +161,8 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Data in: the Account Aggregator (Finvu, I01) and the CAS upload (A10b) only; the app never connects to a broker or a platform directly. Execution out: BSE StAR MF for mutual funds (I02) and smallcase Gateway for stocks, ETFs and REITs through the person's own broker (I03; the supported broker list is Gateway's: to be verified from its documentation). Per connection the app shows: institution, masked account, as-of date, consent valid till, status (connected, failed, stale, expired), include or exclude (A08 fields; consent_status, consent_valid_till, fetch_frequency and last_fetch_at per FIP).</t>
+          <t xml:space="preserve">Data in: the Account Aggregator (Finvu, I01) and the CAS upload (A10b) only; the app never connects to a broker or a platform directly. Execution out: BSE StAR MF for mutual funds (I02) and smallcase Gateway for stocks, ETFs and REITs through the person's own broker (I03; the supported broker list is Gateway's: to be verified from its documentation). Per connection the app shows: institution, masked account, as-of date, consent valid till, status (connected, failed, stale, expired), include or exclude (A08 fields; consent_status, consent_valid_till, fetch_frequency and last_fetch_at per FIP).
+Update, Vatsal, 28 Sep 2026: Finvu, CAS. Execution will be done inside the app itself - using BSE StAR + Smallcase Gateway. Info to be displayed will be shared in 2 weeks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
@@ -386,7 +387,8 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">to be decided: the cancellation and refund rule (brief H5), owner Compliance with Harish (W05). What the board already fixes: cancel is always allowed from Q03a with no reason required; the plan stays readable and refresh stops; pause is offered; a refund request creates a CRM task with the payment reference and lands in S24; the rule itself is a parameter. Note for Compliance: SEBI's investment-adviser fee rules already shape the answer (a refund of the unexpired period on termination, a capped breakage amount); the exact wording is theirs.</t>
+          <t xml:space="preserve">to be decided: the cancellation and refund rule (brief H5), owner Compliance with Harish (W05). What the board already fixes: cancel is always allowed from Q03a with no reason required; the plan stays readable and refresh stops; pause is offered; a refund request creates a CRM task with the payment reference and lands in S24; the rule itself is a parameter. Note for Compliance: SEBI's investment-adviser fee rules already shape the answer (a refund of the unexpired period on termination, a capped breakage amount); the exact wording is theirs.
+Update, Vatsal, 28 Sep 2026: With compliance - will revert in 2 weeks?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
@@ -397,6 +399,11 @@
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">Q03a, S24, W05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
